--- a/docs/User Case.xlsx
+++ b/docs/User Case.xlsx
@@ -4,10 +4,13 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Alle User" sheetId="4" r:id="rId1"/>
+    <sheet name="Verein" sheetId="1" r:id="rId2"/>
+    <sheet name="Sportler" sheetId="2" r:id="rId3"/>
+    <sheet name="Trainer" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,11 +21,154 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>Verein | User Case</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>Beschreibung</t>
+  </si>
+  <si>
+    <t>App</t>
+  </si>
+  <si>
+    <t>Desktop</t>
+  </si>
+  <si>
+    <t>Gastseite öffnen und sehen</t>
+  </si>
+  <si>
+    <t>Alle Benutzer | User Case</t>
+  </si>
+  <si>
+    <t>Sportler | User Case</t>
+  </si>
+  <si>
+    <t>Trainer | User Case</t>
+  </si>
+  <si>
+    <t>Mitgliedschaftsanfrage annehmen Verein</t>
+  </si>
+  <si>
+    <t>Mitgliedschaftsanfrage annehmen Gruppe/Team</t>
+  </si>
+  <si>
+    <t>User zum Mitglied einladen</t>
+  </si>
+  <si>
+    <t>Vereinsmtgliedchsaftsanfragen  senden</t>
+  </si>
+  <si>
+    <t>Teammitgliedschaftsanfrage senden</t>
+  </si>
+  <si>
+    <t>Farbpalette wählen</t>
+  </si>
+  <si>
+    <t>login normal</t>
+  </si>
+  <si>
+    <t>login outlook</t>
+  </si>
+  <si>
+    <t>login gmail</t>
+  </si>
+  <si>
+    <t>Verein + Team anlegen</t>
+  </si>
+  <si>
+    <t>Team X</t>
+  </si>
+  <si>
+    <t>Daten Mitglieder bearbeiten</t>
+  </si>
+  <si>
+    <t>Rolle Mitglieder Team und Verein zuweisen</t>
+  </si>
+  <si>
+    <t>Team + Verein</t>
+  </si>
+  <si>
+    <t>Vereich und Team chat</t>
+  </si>
+  <si>
+    <t>Tabelle Mitglieder Exportieren</t>
+  </si>
+  <si>
+    <t>Events</t>
+  </si>
+  <si>
+    <t>Alle Vereine sehen und filtern Gasseite</t>
+  </si>
+  <si>
+    <t>Mitglieder Beiträge verwalten</t>
+  </si>
+  <si>
+    <t>Mitglieder Notizen</t>
+  </si>
+  <si>
+    <t>Sponsoren verwalten</t>
+  </si>
+  <si>
+    <t>Trikots verkaufe verwalten</t>
+  </si>
+  <si>
+    <t>File manager</t>
+  </si>
+  <si>
+    <t>Geräte und Ressource</t>
+  </si>
+  <si>
+    <t>Ausleih</t>
+  </si>
+  <si>
+    <t>Direkt email schreiben</t>
+  </si>
+  <si>
+    <t>Belege und Abrechnungen
+filemanager (team und verein)
+Galerie und Bilder</t>
+  </si>
+  <si>
+    <t>Kalender</t>
+  </si>
+  <si>
+    <t>Verein + Team bearbeiten</t>
+  </si>
+  <si>
+    <t>verein</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,7 +183,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,15 +191,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -68,8 +256,380 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Grafik 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13573125" y="47625"/>
+          <a:ext cx="2781300" cy="2781300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2433298</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Grafik 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="209550" y="85725"/>
+          <a:ext cx="2423773" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Grafik 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12220575" y="47625"/>
+          <a:ext cx="2781300" cy="2781300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2433298</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Grafik 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="209550" y="85725"/>
+          <a:ext cx="2423773" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Grafik 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13573125" y="47625"/>
+          <a:ext cx="2781300" cy="2781300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2433298</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Grafik 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="209550" y="85725"/>
+          <a:ext cx="2423773" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Grafik 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13573125" y="47625"/>
+          <a:ext cx="2781300" cy="2781300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2433298</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Grafik 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="209550" y="85725"/>
+          <a:ext cx="2423773" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -114,7 +674,7 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -149,7 +709,7 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -331,9 +891,1582 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A5:E36"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="7">
+        <v>0</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="7">
+        <v>-5</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="7">
+        <v>1</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>4</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="7">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>7</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>8</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>9</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>10</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>11</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>12</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>13</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>14</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>15</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>16</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>17</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>18</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>19</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>20</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>21</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>22</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>23</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>24</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>25</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>26</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>27</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>28</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>29</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>30</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:E5"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967294" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{659EE2BF-C2FC-4D1E-AB82-6156099B1B89}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="1"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>D7:E36</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A5:E37"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.42578125" customWidth="1"/>
+    <col min="3" max="3" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="B5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="7">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
+        <v>2</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="7">
+        <v>1</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>3</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="7">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
+        <v>4</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
+        <v>5</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="7">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="8">
+        <v>6</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="7">
+        <v>0</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="8">
+        <v>7</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="7">
+        <v>0</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="8">
+        <v>8</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="7">
+        <v>0</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="8">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="7">
+        <v>0</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="8">
+        <v>10</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="7">
+        <v>0</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="8">
+        <v>11</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="7">
+        <v>0</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
+        <v>12</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="7">
+        <v>0</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="8">
+        <v>13</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="7">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A21" s="8">
+        <v>14</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="7">
+        <v>0</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="8">
+        <v>15</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="7">
+        <v>0</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="8">
+        <v>16</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="7">
+        <v>0</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="8">
+        <v>17</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="7">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="8">
+        <v>18</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="7">
+        <v>0</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="8">
+        <v>19</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="7">
+        <v>0</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="8">
+        <v>20</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="7">
+        <v>0</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="8">
+        <v>21</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="7">
+        <v>0</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
+        <v>22</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="7">
+        <v>0</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="8">
+        <v>23</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="7">
+        <v>0</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="8">
+        <v>24</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="7">
+        <v>0</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="8">
+        <v>25</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="7">
+        <v>0</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="8">
+        <v>26</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="7">
+        <v>0</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="8">
+        <v>27</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="7">
+        <v>0</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="8">
+        <v>28</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="7">
+        <v>0</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="8">
+        <v>29</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="7">
+        <v>0</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="8">
+        <v>30</v>
+      </c>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="7">
+        <v>0</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:E5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967294" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="2" id="{6B144B30-2231-4669-A693-564B7155DDF9}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="1"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>D7:E37</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A5:E36"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>4</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>7</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>8</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>9</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>10</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>11</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>12</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>13</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>14</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>15</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>16</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>17</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>18</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>19</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>20</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>21</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>22</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>23</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>24</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>25</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>26</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>27</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>28</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>29</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>30</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:E5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967294" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{8E908A60-80B8-493C-B1B9-528457A0066F}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="1"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>D7:E36</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A5:E36"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>4</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>7</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>8</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>9</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>10</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>11</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>12</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>13</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>14</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>15</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>16</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>17</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>18</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>19</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>20</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>21</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>22</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>23</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>24</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>25</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>26</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>27</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>28</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>29</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>30</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:E5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967294" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{0F145648-0A6D-4B8E-9545-82D84ECCEB8F}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="1"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>D7:E36</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>